--- a/reports/latest/Failed_Test_Cases.xlsx
+++ b/reports/latest/Failed_Test_Cases.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651932AE-DF42-4945-89A8-63164A684190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Failed Test Cases" state="visible" r:id="rId4"/>
+    <sheet name="Failed Test Cases" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Test ID</t>
   </si>
@@ -32,169 +36,24 @@
   </si>
   <si>
     <t>Screenshot</t>
-  </si>
-  <si>
-    <t>TC_AUTH_010</t>
-  </si>
-  <si>
-    <t>Authentication</t>
-  </si>
-  <si>
-    <t>Invalid OTP Entry Error Message Validation</t>
-  </si>
-  <si>
-    <t>P2 - High</t>
-  </si>
-  <si>
-    <t>OTP validation mismatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error: OTP validation mismatch
-    at main (C:\final_year_project\automation\reports\ReportGeneratorCli.ts:17:66)</t>
-  </si>
-  <si>
-    <t>Screenshots/TC_AUTH_010_failure_1792089843978.png</t>
-  </si>
-  <si>
-    <t>TC_FORM_008</t>
-  </si>
-  <si>
-    <t>Forms</t>
-  </si>
-  <si>
-    <t>Forms Scenario #08: Verification and Edge Case Handling</t>
-  </si>
-  <si>
-    <t>P1 - Critical</t>
-  </si>
-  <si>
-    <t>Validation message missing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error: Validation message missing
-    at main (C:\final_year_project\automation\reports\ReportGeneratorCli.ts:17:66)</t>
-  </si>
-  <si>
-    <t>Screenshots/TC_FORM_008_failure_1792089844116.png</t>
-  </si>
-  <si>
-    <t>TC_CRUD_022</t>
-  </si>
-  <si>
-    <t>CRUD Operations</t>
-  </si>
-  <si>
-    <t>CRUD Operations Scenario #22: Verification and Edge Case Handling</t>
-  </si>
-  <si>
-    <t>P3 - Medium</t>
-  </si>
-  <si>
-    <t>Bulk deletion timeout under heavy database load</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error: Bulk deletion timeout under heavy database load
-    at main (C:\final_year_project\automation\reports\ReportGeneratorCli.ts:17:66)</t>
-  </si>
-  <si>
-    <t>Screenshots/TC_CRUD_022_failure_1792089844176.png</t>
-  </si>
-  <si>
-    <t>TC_VAL_015</t>
-  </si>
-  <si>
-    <t>Input Validation</t>
-  </si>
-  <si>
-    <t>Input Validation Scenario #15: Verification and Edge Case Handling</t>
-  </si>
-  <si>
-    <t>SMILES valence syntax error not surfaced to UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error: SMILES valence syntax error not surfaced to UI
-    at main (C:\final_year_project\automation\reports\ReportGeneratorCli.ts:17:66)</t>
-  </si>
-  <si>
-    <t>Screenshots/TC_VAL_015_failure_1792089844234.png</t>
-  </si>
-  <si>
-    <t>TC_FILE_002</t>
-  </si>
-  <si>
-    <t>File Upload</t>
-  </si>
-  <si>
-    <t>File Upload Scenario #02: Verification and Edge Case Handling</t>
-  </si>
-  <si>
-    <t>P0 - Blocker</t>
-  </si>
-  <si>
-    <t>Application crash on large file buffer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error: Application crash on large file buffer
-    at main (C:\final_year_project\automation\reports\ReportGeneratorCli.ts:17:66)</t>
-  </si>
-  <si>
-    <t>Screenshots/TC_FILE_002_failure_1792089844287.png</t>
-  </si>
-  <si>
-    <t>TC_OFFL_004</t>
-  </si>
-  <si>
-    <t>Offline Handling</t>
-  </si>
-  <si>
-    <t>Offline Handling Scenario #04: Verification and Edge Case Handling</t>
-  </si>
-  <si>
-    <t>Offline cache sync conflict on network reconnection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error: Offline cache sync conflict on network reconnection
-    at main (C:\final_year_project\automation\reports\ReportGeneratorCli.ts:17:66)</t>
-  </si>
-  <si>
-    <t>Screenshots/TC_OFFL_004_failure_1792089844317.png</t>
-  </si>
-  <si>
-    <t>TC_A11Y_007</t>
-  </si>
-  <si>
-    <t>Accessibility</t>
-  </si>
-  <si>
-    <t>Accessibility Scenario #07: Verification and Edge Case Handling</t>
-  </si>
-  <si>
-    <t>Accessibility label missing on molecular 3D interactive viewport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error: Accessibility label missing on molecular 3D interactive viewport
-    at main (C:\final_year_project\automation\reports\ReportGeneratorCli.ts:17:66)</t>
-  </si>
-  <si>
-    <t>Screenshots/TC_A11Y_007_failure_1792089844345.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFF"/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Segoe UI"/>
     </font>
   </fonts>
@@ -207,7 +66,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="991B1B"/>
+        <fgColor rgb="FF991B1B"/>
       </patternFill>
     </fill>
   </fills>
@@ -221,16 +80,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="CBD5E1"/>
+        <color rgb="FFCBD5E1"/>
       </left>
       <right style="thin">
-        <color rgb="CBD5E1"/>
+        <color rgb="FFCBD5E1"/>
       </right>
       <top style="thin">
-        <color rgb="CBD5E1"/>
+        <color rgb="FFCBD5E1"/>
       </top>
       <bottom style="medium">
-        <color rgb="94A3B8"/>
+        <color rgb="FF94A3B8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -581,9 +440,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -592,7 +451,7 @@
     <col min="5" max="7" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -613,171 +472,10 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>